--- a/results/job_matches_2026-09-06.xlsx
+++ b/results/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Developer (Sr. Software Development Engineer)</t>
+          <t>Senior AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Hadoop, HBase, Spark, Scala, Kafka, Kafka Connect</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022f538ee963f0fc</t>
+          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
         </is>
       </c>
     </row>
@@ -648,160 +648,160 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, SQS, Google Cloud Platform, GCP, BigQuery, Hive, MongoDB</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ece101fdd46d43</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
+          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, HDFS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98502872a41fe5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd968ee3884958</t>
+          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,137 +811,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc818fd6890b2dec</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a27379fe391fa5a</t>
+          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer</t>
+          <t>Software Engineer II - Platform Engineer Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AIT Worldwide Logistics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Itasca, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0a712c62866b60</t>
+          <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sudsies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
+          <t>Senior Architect Data Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,742 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2271198a574d9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Evans Transportation Services</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Delafield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Advisor II, Application Architecture- Refining</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Phillips 66</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Bartlesville, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Data Factory, Databricks, Scala, NoSQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8713f75756bef7c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40f32a3160c1474</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Temporal Technologies</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfd7828f198d4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Temporal Technologies</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4431f9fbff54b677</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud Platform Foundations</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Temporal Technologies</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1005fb477c4a6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GenAI Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Finbott</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b778056e6432a80</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Full Stack Intern</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Keysight Technologies</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer Databricks</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Container Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Plymouth Meeting, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb597ffd634147d</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19d4e1e77e48b014</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba99f796c7872860</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Architect Data Management</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e993627069df064a</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd083e076d8b8502</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dac506ae75c0be97</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f824b47d59a23e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=614c4f0911550465</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e28b34ca0baae4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-06.xlsx
+++ b/results/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,47 +503,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Personify Health</t>
+          <t>Sudsies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aface31a02c74f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9faddc3559ec4193</t>
+          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI/Data Science Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33851c58406093cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de1c6e7b53b6594</t>
+          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sudsies</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,287 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
+          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
+          <t>Software Engineer II - Platform Engineer Databricks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Full-Stack AI Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Juan, PR, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Evans Transportation Services</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Delafield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Full Stack Intern</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Keysight Technologies</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0aa7a5c969525f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer Databricks</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Container Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0ae1ea15db8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Architect Data Management</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fort Washington, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a21b73928bb91d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-06.xlsx
+++ b/results/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Hadoop</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383bce16ad78ce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sudsies</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365403b2fe630d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
+          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
+          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Platform Engineer Databricks</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -635,76 +635,6 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer Databricks</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
         </is>

--- a/results/job_matches_2026-09-06.xlsx
+++ b/results/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SENIOR TABLEAU ANALYTICS ENGINEER</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, SQL Server, Fact Tables, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e10a214d6bc15f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Evans Transportation Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Delafield, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
+          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
+          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer II - Platform Engineer Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -600,41 +600,6 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer Databricks</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
         </is>

--- a/results/job_matches_2026-09-06.xlsx
+++ b/results/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,41 +567,6 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer Databricks</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-06.xlsx
+++ b/results/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evans Transportation Services</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Delafield, WI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -530,41 +530,6 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
         </is>
